--- a/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/opex.xlsx
+++ b/PlanetTEK_Portal_server/doc_test/table_creators/tables/xlsx1/opex.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>1.233 ₺ /yıl</t>
+          <t>1.233 € /yıl</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>36 ₺ /yıl</t>
+          <t>36 € /yıl</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>1.269 ₺ /yıl</t>
+          <t>1.269 € /yıl</t>
         </is>
       </c>
     </row>
